--- a/out/MLP-Mamba1_repeat_1_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.633306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.233306561630227</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.633306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7138070993914605</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7138070993914605</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.000356359406394884</v>
+        <v>-0.0003187095611483092</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4586623150920038</v>
+        <v>0.4102038210157579</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.233306561630227</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9181926399135468</v>
+        <v>0.8211843668648274</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1059239810575001</v>
+        <v>-0.09473302018338621</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3523819746281088</v>
+        <v>0.3151520912712235</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.233306561630227</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3523819746281088</v>
+        <v>0.3151520912712235</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.233306561630227</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3519922083080998</v>
+        <v>0.3148759057201962</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.19744626729591</v>
+        <v>0.8485017432176496</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.749269463479246</v>
+        <v>2.013568957444796</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2291178508372719</v>
+        <v>0.1623511858441944</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.633306561630227</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.008311258729316</v>
+        <v>1.488531488042106</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4013216448407176</v>
+        <v>0.2843734990823945</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.633306561630227</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.581949320728867</v>
+        <v>1.895007195012356</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.219778575310485</v>
+        <v>0.1557332766185505</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.233306561630227</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.619838476051484</v>
+        <v>1.92185517790611</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.09077175230178069</v>
+        <v>0.0643203080432633</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.5813730088882</v>
+        <v>1.894598783331452</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1130938138610675</v>
+        <v>0.08013758422496202</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.71680411994076</v>
+        <v>1.990564439613833</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.06809649394743847</v>
+        <v>0.04825258667233542</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.739827730757266</v>
+        <v>2.006878829586493</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05177253967961519</v>
+        <v>0.03668583554762436</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.233306561630227</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.775246036014459</v>
+        <v>2.031976113399142</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02289912903417543</v>
+        <v>0.01622624053465855</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.233306561630227</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.769226091984594</v>
+        <v>2.027710402695124</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0181693706185043</v>
+        <v>0.01287341351847365</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.233306561630227</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.782659980561601</v>
+        <v>2.037228638609014</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.009007833388688085</v>
+        <v>0.006381279112217785</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.633306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.782494103097988</v>
+        <v>2.037109638620425</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005237379743624433</v>
+        <v>0.003710049352168924</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.633306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.783953766027672</v>
+        <v>2.038142582328087</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002616189871812217</v>
+        <v>0.001851070075711647</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.783945502469337</v>
+        <v>2.038135271395548</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001288591673071766</v>
+        <v>0.000912012763799763</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.633306561630227</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.783907721901414</v>
+        <v>2.038107023544451</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0007459718750281157</v>
+        <v>0.0005290244444644378</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.784110857057088</v>
+        <v>2.038249701122964</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002472126228788256</v>
+        <v>0.0001735576091177526</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.783855355193342</v>
+        <v>2.038067354670754</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001207643042471784</v>
+        <v>8.483164589084172e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.633306561630227</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.783851760640701</v>
+        <v>2.038063348677698</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.349349164303817e-05</v>
+        <v>4.392392260217012e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.783858111604302</v>
+        <v>2.038066313190443</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.818252625748566e-05</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.233306561630227</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.783850862857269</v>
+        <v>2.038059761304713</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.536440521940679e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.783853932520712</v>
+        <v>2.038060139872958</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.783846262799617</v>
+        <v>2.038053472909088</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.783842777579309</v>
+        <v>2.038049610833992</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.783838230267124</v>
+        <v>2.038045063521807</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.783838320211774</v>
+        <v>2.038045153466457</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.783837462278189</v>
+        <v>2.038044295532872</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.783837690599224</v>
+        <v>2.038044523853906</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.783836894935012</v>
+        <v>2.038043728189695</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.783836957204385</v>
+        <v>2.038043790459068</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>2.233306561630227</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.783836984879662</v>
+        <v>2.038043818134345</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.233306561630227</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.783837137093685</v>
+        <v>2.038043970348367</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.783836791152724</v>
+        <v>2.038043624407406</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.783836867259735</v>
+        <v>2.038043700514418</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.783837033311397</v>
+        <v>2.038043866566079</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.783837393089997</v>
+        <v>2.038044226344679</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.233306561630227</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.783837413846455</v>
+        <v>2.038044247101137</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.783837517628743</v>
+        <v>2.038044350883425</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.783837745949778</v>
+        <v>2.03804457920446</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.783837621411032</v>
+        <v>2.038044454665714</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.783837649086309</v>
+        <v>2.038044482340991</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.633306561630227</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.783837704436862</v>
+        <v>2.038044537691545</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.783837967351993</v>
+        <v>2.038044800606675</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.783837884326162</v>
+        <v>2.038044717580845</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.783837676761585</v>
+        <v>2.038044510016268</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.783837690599224</v>
+        <v>2.038044523853906</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.783837828975609</v>
+        <v>2.038044662230291</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.78383754530402</v>
+        <v>2.038044378558702</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.783837372333539</v>
+        <v>2.038044205588222</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.783837268551251</v>
+        <v>2.038044101805933</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.783837413846455</v>
+        <v>2.038044247101137</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.783837656005128</v>
+        <v>2.03804448925981</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.783837483034647</v>
+        <v>2.03804431628933</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.78383718552542</v>
+        <v>2.038044018780103</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.783837171687781</v>
+        <v>2.038044004942464</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.783836804990362</v>
+        <v>2.038043638245044</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.783836804990362</v>
+        <v>2.038043638245044</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.783836742720989</v>
+        <v>2.038043575975671</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.7838366389387</v>
+        <v>2.038043472193383</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.78383646596822</v>
+        <v>2.038043299222902</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.783836514399954</v>
+        <v>2.038043347654637</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.783836154621354</v>
+        <v>2.038042987876037</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.783836113108439</v>
+        <v>2.038042946363121</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.783836168458993</v>
+        <v>2.038043001713675</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.783836223809547</v>
+        <v>2.038043057064229</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.783836265322462</v>
+        <v>2.038043098577145</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.783835995488512</v>
+        <v>2.038042828743194</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.783836050839065</v>
+        <v>2.038042884093748</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.78383619613427</v>
+        <v>2.038043029388952</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.783836161540174</v>
+        <v>2.038042994794856</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.783836147702535</v>
+        <v>2.038042980957218</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.783836237647185</v>
+        <v>2.038043070901868</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.233306561630227</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.783836555912869</v>
+        <v>2.038043389167552</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.78383637602357</v>
+        <v>2.038043209278252</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.783836417536485</v>
+        <v>2.038043250791167</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.783836230728366</v>
+        <v>2.038043063983048</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.783836299916558</v>
+        <v>2.03804313317124</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.7838360992708</v>
+        <v>2.038042932525483</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.783836140783716</v>
+        <v>2.038042974038398</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.783836168458993</v>
+        <v>2.038043001713675</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_1_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.633306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.5351820110112873</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.5351820110112873</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.633306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.5351820110112873</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.000356359406394884</v>
+        <v>-0.0002705418227438349</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4586623150920038</v>
+        <v>0.3482084000650801</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9181926399135468</v>
+        <v>0.6970757779210504</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1059239810575001</v>
+        <v>-0.08041563206507914</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3523819746281088</v>
+        <v>0.267522226177257</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3523819746281088</v>
+        <v>0.267522226177257</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3519922083080998</v>
+        <v>0.2673087304148981</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.19744626729591</v>
+        <v>0.6559051545500256</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.749269463479246</v>
+        <v>1.580425099981012</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2291178508372719</v>
+        <v>0.1254999987142992</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.633306561630227</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.008311258729316</v>
+        <v>1.174562902015506</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4013216448407176</v>
+        <v>0.219825149928201</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.633306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.581949320728867</v>
+        <v>1.488775033638726</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.219778575310485</v>
+        <v>0.1203842516688374</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.619838476051484</v>
+        <v>1.509528952564095</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.09077175230178069</v>
+        <v>0.04972044912968192</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.5813730088882</v>
+        <v>1.488459315906831</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1130938138610675</v>
+        <v>0.06194790331420083</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.71680411994076</v>
+        <v>1.562642625203706</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.06809649394743847</v>
+        <v>0.03730063975240949</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.739827730757266</v>
+        <v>1.57525396359822</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05177253967961519</v>
+        <v>0.02835761565952419</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.775246036014459</v>
+        <v>1.594654413609786</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02289912903417543</v>
+        <v>0.01254246085761289</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.769226091984594</v>
+        <v>1.591355891893292</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0181693706185043</v>
+        <v>0.009950170026912553</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.782659980561601</v>
+        <v>1.598712680907232</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.009007833388688085</v>
+        <v>0.004932922039764163</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.633306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.782494103097988</v>
+        <v>1.598619551254185</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005237379743624433</v>
+        <v>0.002866381135936357</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.633306561630227</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.783953766027672</v>
+        <v>1.599416783391587</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002616189871812217</v>
+        <v>0.001429235967595364</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.783945502469337</v>
+        <v>1.599409997670989</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001288591673071766</v>
+        <v>0.0007050380961082805</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.633306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.783907721901414</v>
+        <v>1.5993870237698</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0007459718750281157</v>
+        <v>0.0004055312916820366</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.784110857057088</v>
+        <v>1.599496014469171</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002472126228788256</v>
+        <v>0.0001333821470662583</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.783855355193342</v>
+        <v>1.599353570968708</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001207643042471784</v>
+        <v>6.461952556540234e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.633306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.783851760640701</v>
+        <v>1.599349341324089</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.349349164303817e-05</v>
+        <v>3.169294195162759e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.783858111604302</v>
+        <v>1.599350515354406</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.818252625748566e-05</v>
+        <v>1.396144357570609e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.233306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.783850862857269</v>
+        <v>1.599344273845822</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.536440521940679e-05</v>
+        <v>6.636802982518164e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.783853932520712</v>
+        <v>1.599343576700418</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.783846262799617</v>
+        <v>1.599337241839871</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.783842777579309</v>
+        <v>1.599332999229717</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.783838230267124</v>
+        <v>1.599333227550752</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.783838320211774</v>
+        <v>1.599333317495402</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.783837462278189</v>
+        <v>1.599332459561817</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.783837690599224</v>
+        <v>1.599332687882852</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.783836894935012</v>
+        <v>1.59933189221864</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.783836957204385</v>
+        <v>1.599331954488013</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>2.233306561630227</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.783836984879662</v>
+        <v>1.59933198216329</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.783837137093685</v>
+        <v>1.599332134377313</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.783836791152724</v>
+        <v>1.599331788436351</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.783836867259735</v>
+        <v>1.599331864543363</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.783837033311397</v>
+        <v>1.599332030595024</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.783837393089997</v>
+        <v>1.599332390373624</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.783837413846455</v>
+        <v>1.599332411130082</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.783837517628743</v>
+        <v>1.59933251491237</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.783837745949778</v>
+        <v>1.599332743233405</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.783837621411032</v>
+        <v>1.599332618694659</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.783837649086309</v>
+        <v>1.599332646369936</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.633306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.783837704436862</v>
+        <v>1.59933270172049</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.783837967351993</v>
+        <v>1.599332964635621</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.783837884326162</v>
+        <v>1.59933288160979</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.783837676761585</v>
+        <v>1.599332674045213</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.783837690599224</v>
+        <v>1.599332687882852</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.783837828975609</v>
+        <v>1.599332826259236</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.78383754530402</v>
+        <v>1.599332542587648</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.783837372333539</v>
+        <v>1.599332369617167</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.783837268551251</v>
+        <v>1.599332265834879</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.783837413846455</v>
+        <v>1.599332411130082</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.783837656005128</v>
+        <v>1.599332653288756</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.5351820110112873</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.783837483034647</v>
+        <v>1.599332480318275</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.78383718552542</v>
+        <v>1.599332182809048</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.783837171687781</v>
+        <v>1.599332168971409</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.783836804990362</v>
+        <v>1.59933180227399</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.233306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.783836804990362</v>
+        <v>1.59933180227399</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.783836742720989</v>
+        <v>1.599331740004617</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.7838366389387</v>
+        <v>1.599331636222328</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.78383646596822</v>
+        <v>1.599331463251847</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.783836514399954</v>
+        <v>1.599331511683582</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.783836154621354</v>
+        <v>1.599331151904982</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.783836113108439</v>
+        <v>1.599331110392067</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.783836168458993</v>
+        <v>1.59933116574262</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.783836223809547</v>
+        <v>1.599331221093174</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.783836265322462</v>
+        <v>1.59933126260609</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.783835995488512</v>
+        <v>1.59933099277214</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.783836050839065</v>
+        <v>1.599331048122693</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.78383619613427</v>
+        <v>1.599331193417898</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.783836161540174</v>
+        <v>1.599331158823801</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.783836147702535</v>
+        <v>1.599331144986163</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.783836237647185</v>
+        <v>1.599331234930813</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.783836555912869</v>
+        <v>1.599331553196497</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.78383637602357</v>
+        <v>1.599331373307197</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.5351820110112873</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.783836417536485</v>
+        <v>1.599331414820113</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.783836230728366</v>
+        <v>1.599331228011994</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.783836299916558</v>
+        <v>1.599331297200186</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.7838360992708</v>
+        <v>1.599331096554428</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.783836140783716</v>
+        <v>1.599331138067344</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.783836168458993</v>
+        <v>1.59933116574262</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_1_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4689014852046967</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.02000000000000013</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4699021577835083</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.09000000000000008</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4807901382446289</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.06155603134918715</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5112699270248413</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.06155603134918715</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.434821605682373</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.5001969933509827</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4330505430698395</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4896239042282104</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4967319071292877</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4298467040061951</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4542335867881775</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4293532371520996</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4999053776264191</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4197322726249695</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4160232543945312</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4146840870380402</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4725667536258698</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4858774542808533</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.5244573950767517</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4477421641349792</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4092741012573242</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5351820110112873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4235055446624756</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.5351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4227273464202881</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5254966020584106</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4086999893188477</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.590342104434967</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.812069948312913</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.5449333190917969</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.485695927975013</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5095819234848022</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.812069948312913</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4357849657535553</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4856245219707489</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.3994269371032715</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3791267275810242</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.431228369474411</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5490821003913879</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4501615762710571</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4407239258289337</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5107500553131104</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4022042751312256</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4396401345729828</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5351820110112873</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4778772294521332</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.06155603134918715</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5747300386428833</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.812069948312913</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6136157512664795</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.485695927975013</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6349620223045349</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.485695927975013</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002705418227438349</v>
+        <v>-0.0001826481971237809</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3482084000650801</v>
+        <v>0.2350824573080914</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.5037379264831543</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.812069948312913</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6970757779210504</v>
+        <v>0.4706098037066381</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08041563206507914</v>
+        <v>-0.05429020204081502</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.357615739107132</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.267522226177257</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5727050304412842</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.812069948312913</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.267522226177257</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.5815160870552063</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.812069948312913</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2673087304148981</v>
+        <v>0.1805353231967278</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.6559051545500256</v>
+        <v>0.2282159622144663</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4378370642662048</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.812069948312913</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.580425099981012</v>
+        <v>0.6374220041313774</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1254999987142992</v>
+        <v>0.04366655291131923</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.6111524701118469</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.6120699483129129</v>
+        <v>-0.16</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.174562902015506</v>
+        <v>0.4962059105595811</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.219825149928201</v>
+        <v>0.07648632621329152</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5453967452049255</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.485695927975013</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.488775033638726</v>
+        <v>0.6055332909506734</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1203842516688374</v>
+        <v>0.04188645735538458</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.5033882856369019</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.485695927975013</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.509528952564095</v>
+        <v>0.6127544298176431</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04972044912968192</v>
+        <v>0.01729971689228928</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.6117337346076965</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.485695927975013</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.488459315906831</v>
+        <v>0.6054234131568402</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.06194790331420083</v>
+        <v>0.02155396268611361</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.6820259094238281</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.485695927975013</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.562642625203706</v>
+        <v>0.6312351134164363</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03730063975240949</v>
+        <v>0.01297810855661497</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.6472271084785461</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.485695927975013</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.57525396359822</v>
+        <v>0.6356225115857507</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02835761565952419</v>
+        <v>0.009865561962379997</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.5766227841377258</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.485695927975013</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.594654413609786</v>
+        <v>0.6423710901332695</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01254246085761289</v>
+        <v>0.004360785304099126</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.5854009985923767</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.485695927975013</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.591355891893292</v>
+        <v>0.641220136472065</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.009950170026912553</v>
+        <v>0.0034579968195974</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.5339934825897217</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.485695927975013</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.598712680907232</v>
+        <v>0.6437766111456487</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.004932922039764163</v>
+        <v>0.001713516940890567</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.7823169827461243</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.485695927975013</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.598619551254185</v>
+        <v>0.6437409398834182</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002866381135936357</v>
+        <v>0.0009928558557509325</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.7432575821876526</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.6120699483129129</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.599416783391587</v>
+        <v>0.6440151379854742</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001429235967595364</v>
+        <v>0.000495382528248281</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.3511255979537964</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.6120699483129129</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.599409997670989</v>
+        <v>0.6440095149754481</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0007050380961082805</v>
+        <v>0.0002422197419648264</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.6360477209091187</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.5993870237698</v>
+        <v>0.6439982568560056</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0004055312916820366</v>
+        <v>0.0001385190694498177</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.2855600118637085</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.599496014469171</v>
+        <v>0.6440329452052312</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001333821470662583</v>
+        <v>4.187137239341006e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.430681973695755</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.599353570968708</v>
+        <v>0.643980284750449</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>6.461952556540234e-05</v>
+        <v>1.970370261998147e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.5170406699180603</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.599349341324089</v>
+        <v>0.6439755581023584</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>3.169294195162759e-05</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.4252635836601257</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.6120699483129129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.599350515354406</v>
+        <v>0.6439727498763025</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.396144357570609e-05</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.6818057894706726</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.599344273845822</v>
+        <v>0.6439672843105835</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.636802982518164e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4500478804111481</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.812069948312913</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.599343576700418</v>
+        <v>0.6439638996921326</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.6279920935630798</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.599337241839871</v>
+        <v>0.6439582322618589</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.6722877025604248</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.812069948312913</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.599332999229717</v>
+        <v>0.6439586127969166</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.3672200739383698</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.16</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.599333227550752</v>
+        <v>0.6439588411179513</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.2510359883308411</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.599333317495402</v>
+        <v>0.6439589310626013</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.4701430797576904</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.599332459561817</v>
+        <v>0.6439580731290164</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.3192548751831055</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.599332687882852</v>
+        <v>0.6439583014500512</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4901917278766632</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.59933189221864</v>
+        <v>0.6439575057858394</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4103750586509705</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.599331954488013</v>
+        <v>0.6439575680552125</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.5008609294891357</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.6120699483129129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.59933198216329</v>
+        <v>0.6439575957304894</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.5301258563995361</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.812069948312913</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.599332134377313</v>
+        <v>0.6439577479445127</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.4111779630184174</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.812069948312913</v>
+        <v>0.16</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.599331788436351</v>
+        <v>0.6439574020035509</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.5499497652053833</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.599331864543363</v>
+        <v>0.6439574781105626</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3931808471679688</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.599332030595024</v>
+        <v>0.6439576441622241</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.6743627786636353</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.812069948312913</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.599332390373624</v>
+        <v>0.6439580039408241</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5726880431175232</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.485695927975013</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.599332411130082</v>
+        <v>0.6439580246972819</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.6824575066566467</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.59933251491237</v>
+        <v>0.6439581284795703</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.4692427814006805</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.599332743233405</v>
+        <v>0.6439583568006051</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.442065954208374</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.599332618694659</v>
+        <v>0.6439582322618589</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.4565969407558441</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.599332646369936</v>
+        <v>0.6439582599371357</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.661374032497406</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.59933270172049</v>
+        <v>0.6439583152876897</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3491125106811523</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.599332964635621</v>
+        <v>0.6439585782028204</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4774697124958038</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.59933288160979</v>
+        <v>0.6439584951769896</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4985528886318207</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.599332674045213</v>
+        <v>0.6439582876124128</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4932706356048584</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.599332687882852</v>
+        <v>0.6439583014500512</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.4045747518539429</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.599332826259236</v>
+        <v>0.6439584398264359</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3495056629180908</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.599332542587648</v>
+        <v>0.6439581561548472</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3804889917373657</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.06155603134918715</v>
+        <v>0.16</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.599332369617167</v>
+        <v>0.6439579831843665</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.6032867431640625</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.812069948312913</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.599332265834879</v>
+        <v>0.6439578794020779</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.5458970665931702</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.812069948312913</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.599332411130082</v>
+        <v>0.6439580246972819</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.45189568400383</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.599332653288756</v>
+        <v>0.6439582668559551</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.2871712148189545</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.599332480318275</v>
+        <v>0.6439580938854741</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4181594550609589</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.599332182809048</v>
+        <v>0.6439577963762472</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.2808825969696045</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.599332168971409</v>
+        <v>0.6439577825386087</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.4084872007369995</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.59933180227399</v>
+        <v>0.6439574158411895</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.5354644060134888</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.59933180227399</v>
+        <v>0.6439574158411895</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.3735418319702148</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.599331740004617</v>
+        <v>0.6439573535718164</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3636168837547302</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.599331636222328</v>
+        <v>0.6439572497895278</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4107290208339691</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.599331463251847</v>
+        <v>0.6439570768190471</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3268875479698181</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.599331511683582</v>
+        <v>0.6439571252507816</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3290534615516663</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.599331151904982</v>
+        <v>0.6439567654721816</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4057804346084595</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.599331110392067</v>
+        <v>0.6439567239592662</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4582620561122894</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.59933116574262</v>
+        <v>0.6439567793098199</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3453654050827026</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.599331221093174</v>
+        <v>0.6439568346603739</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3194157183170319</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.16</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.59933126260609</v>
+        <v>0.6439568761732892</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3217917680740356</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.59933099277214</v>
+        <v>0.6439566063393392</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.4369864761829376</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.599331048122693</v>
+        <v>0.6439566616898931</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3446640074253082</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.599331193417898</v>
+        <v>0.6439568069850971</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4040278494358063</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.16</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.599331158823801</v>
+        <v>0.6439567723910008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3320487141609192</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.599331144986163</v>
+        <v>0.6439567585533622</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.6299470067024231</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.812069948312913</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.599331234930813</v>
+        <v>0.6439568484980124</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.654443085193634</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.812069948312913</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.599331553196497</v>
+        <v>0.6439571667636971</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.3644552528858185</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.599331373307197</v>
+        <v>0.643956986874397</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.3951025009155273</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5351820110112873</v>
+        <v>0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.599331414820113</v>
+        <v>0.6439570283873123</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4705838561058044</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.599331228011994</v>
+        <v>0.643956841579193</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3162358105182648</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.599331297200186</v>
+        <v>0.6439569107673855</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4118990004062653</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.599331096554428</v>
+        <v>0.6439567101216277</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3939346373081207</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.599331138067344</v>
+        <v>0.643956751634543</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4748214483261108</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.2999999999999999</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.59933116574262</v>
+        <v>0.6439567793098199</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_1_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000006.xlsx
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.5244573950767517</v>
+        <v>0.5244573354721069</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.5339934825897217</v>
+        <v>0.5339934229850769</v>
       </c>
       <c r="JB58" t="n">
         <v>0.8599999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.7823169827461243</v>
+        <v>0.7823168635368347</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.02000000000000007</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.3511255979537964</v>
+        <v>0.3511256575584412</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.1600000000000001</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.2855600118637085</v>
+        <v>0.2855599820613861</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.4252635836601257</v>
+        <v>0.4252634942531586</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.6818057894706726</v>
+        <v>0.6818057298660278</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.4399999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.6722877025604248</v>
+        <v>0.67228764295578</v>
       </c>
       <c r="JB70" t="n">
         <v>0.1600000000000001</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.2510359883308411</v>
+        <v>0.2510359585285187</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.4701430797576904</v>
+        <v>0.470143049955368</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.5301258563995361</v>
+        <v>0.5301257967948914</v>
       </c>
       <c r="JB78" t="n">
         <v>0.1600000000000001</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.4692427814006805</v>
+        <v>0.4692427217960358</v>
       </c>
       <c r="JB85" t="n">
         <v>0.16</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.3491125106811523</v>
+        <v>0.34911248087883</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.4399999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.4985528886318207</v>
+        <v>0.4985528290271759</v>
       </c>
       <c r="JB91" t="n">
         <v>0.1600000000000001</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.3495056629180908</v>
+        <v>0.3495056927204132</v>
       </c>
       <c r="JB94" t="n">
         <v>0.16</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.3268875479698181</v>
+        <v>0.3268875777721405</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.3194157183170319</v>
+        <v>0.3194156885147095</v>
       </c>
       <c r="JB112" t="n">
         <v>0.16</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.3217917680740356</v>
+        <v>0.3217917382717133</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.1199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.4369864761829376</v>
+        <v>0.4369864165782928</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.1199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.3320487141609192</v>
+        <v>0.3320487439632416</v>
       </c>
       <c r="JB117" t="n">
         <v>0.16</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.3951025009155273</v>
+        <v>0.3951025605201721</v>
       </c>
       <c r="JB121" t="n">
         <v>0.16</v>
